--- a/ExitGame_LevelSteps.xlsx
+++ b/ExitGame_LevelSteps.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hunde\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15AA1FFB-57C1-46AB-B480-754ED60A1126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD287BE-E44A-40F6-A2B9-E3D472812016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C76EBBFD-2312-4589-BC35-AF319542F9C4}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="347">
   <si>
     <t>Exit Game Level Steps</t>
   </si>
@@ -87,9 +87,6 @@
     <t>ContainerInteractable_Chest</t>
   </si>
   <si>
-    <t>Finde den Schlüssel für die Kinderzimmertür.</t>
-  </si>
-  <si>
     <t>1_01_KEY_OBTAINED</t>
   </si>
   <si>
@@ -105,9 +102,6 @@
     <t>1_01_DOOR_USED</t>
   </si>
   <si>
-    <t>KEY_CHILDREN</t>
-  </si>
-  <si>
     <t>1_01_REMOVE_BS</t>
   </si>
   <si>
@@ -120,9 +114,6 @@
     <t>1_01_INTRO_COMPLETED</t>
   </si>
   <si>
-    <t>StoryInteractable_ClosetLocked, StoryInteractable_Bed, StoryInteractable_DrawerLocked, StoryInteractable_DoorLocked, BlackscreenInteractable_Lvl1Intro, StoryInteractable_PC</t>
-  </si>
-  <si>
     <t>1_02_HUNGRYPT1_FIN</t>
   </si>
   <si>
@@ -165,9 +156,6 @@
     <t>1_03_HUNGRYPT2_FIN</t>
   </si>
   <si>
-    <t>DoorInteractable_ToLiving, DoorInteractable_To2FCorridor, StoryInteractable_CellarLockedLvl1</t>
-  </si>
-  <si>
     <t>1_03_ENTERINGLIVING</t>
   </si>
   <si>
@@ -177,9 +165,6 @@
     <t>1_04_PREPARE_LIVING</t>
   </si>
   <si>
-    <t>StoryInteractable_FridgePart1, StoryInteractable_StorageLocked, StoryInteractable_TV, StoryInteractable_Plant, LockInteractable_ClosetDummy, DoorInteractable_To1FCorridor</t>
-  </si>
-  <si>
     <t>Gehe in die Küche und suche im Kühlschrank nach Essen.</t>
   </si>
   <si>
@@ -207,9 +192,6 @@
     <t>KEY_STORAGE</t>
   </si>
   <si>
-    <t>StoryInteractable_StorageKeyObtained, ContainerInteractable_Storage</t>
-  </si>
-  <si>
     <t>1_04_GENJEKKOLINESSWAP</t>
   </si>
   <si>
@@ -246,9 +228,6 @@
     <t>StoryInteractable_PhoneNoCable</t>
   </si>
   <si>
-    <t>StoryInteractable_StorageLockedJekko</t>
-  </si>
-  <si>
     <t>PIZZA_NUMBER</t>
   </si>
   <si>
@@ -270,9 +249,6 @@
     <t>StoryInteractable_StorageKeyObtained</t>
   </si>
   <si>
-    <t>StoryInteractable_DrawerLockedJekko</t>
-  </si>
-  <si>
     <t>1_05_PIZZANUM_OBTAINED</t>
   </si>
   <si>
@@ -345,9 +321,6 @@
     <t>1_08_PREPAREPHONE</t>
   </si>
   <si>
-    <t>StoryInteractable_PuzzleFinished, StoryInteractable_PhoneGenericLvl1</t>
-  </si>
-  <si>
     <t>DoorInteractable_AutoLvlFin</t>
   </si>
   <si>
@@ -381,9 +354,6 @@
     <t>2_01_POSTPIZZAFIN</t>
   </si>
   <si>
-    <t>Gehe zum Telefon und bestell dir und Jekko eine Pizza.</t>
-  </si>
-  <si>
     <t>Verlasse das Badezimmer.</t>
   </si>
   <si>
@@ -417,9 +387,6 @@
     <t>2_02_PREPARE_2FCORR</t>
   </si>
   <si>
-    <t>DoorInteractable_To2FBathroom, StoryInteractable_3rdFloorLockedLvl2, ContainerInteractable_DrawerBath2F</t>
-  </si>
-  <si>
     <t>StoryInteractable_ShadowEncounter1, StoryInteractable_3rdFloorLockedJekko</t>
   </si>
   <si>
@@ -435,9 +402,6 @@
     <t>DoorInteractable_To2FBathroom, StoryInteractable_3rdFloorLockedLvl2</t>
   </si>
   <si>
-    <t>StoryInteractable_ScissorsFound, BlackscreenInteractable_3FOn</t>
-  </si>
-  <si>
     <t>2_02_SCISSORSFOUNDFIN</t>
   </si>
   <si>
@@ -453,15 +417,6 @@
     <t>2_02_FGSWAP</t>
   </si>
   <si>
-    <t>SpriteToggleInteractable_Chain, SpriteToggleInteractable_OldFG, SpriteToggleInteractable_NewFG</t>
-  </si>
-  <si>
-    <t>2_02_FGSWAP_FIN</t>
-  </si>
-  <si>
-    <t>SpriteToggleInteractable_NewFG</t>
-  </si>
-  <si>
     <t>2_02_REMOVE_BS</t>
   </si>
   <si>
@@ -510,9 +465,6 @@
     <t>2_03_PREPARE_CORR</t>
   </si>
   <si>
-    <t>StoryInteractable_ShadowEncounter2, ReadableInteractable_Remember</t>
-  </si>
-  <si>
     <t>StoryInteractable_Picture1, StoryInteractable_Picture2, StoryInteractable_Picture3, StoryInteractable_Picture4, StoryInteractable_FatherPart1, StoryInteractable_3FBathLocked, DoorInteractable_To2FCorridor</t>
   </si>
   <si>
@@ -528,9 +480,6 @@
     <t>2_03_FATHERCUTSCENE</t>
   </si>
   <si>
-    <t>ReadableInteractable_Remember, StoryInteractable_FatherPart2</t>
-  </si>
-  <si>
     <t>Gehe in den Keller.</t>
   </si>
   <si>
@@ -540,9 +489,6 @@
     <t>StoryInteractable_FatherPart2</t>
   </si>
   <si>
-    <t>ReadableInteractable_Remember, StoryInteractable_FatherPart2, StoryInteractable_CellarLockedLvl1Jekko</t>
-  </si>
-  <si>
     <t>ReadableInteractive_RememberMAN, StoryInteractable_CellarLockedLvl2CS</t>
   </si>
   <si>
@@ -729,13 +675,397 @@
     <t>2_07_POSTHORROR_CSFIN</t>
   </si>
   <si>
-    <t>2_07_PREPARE_2FCORR</t>
-  </si>
-  <si>
     <t>Finde etwas, um den Schlüssel für das Schlafzimmer von Papa zu reparieren.</t>
   </si>
   <si>
-    <t>StoryInteractable_ParentClosedLvl1Jekko</t>
+    <t>DragItemZone_UnlockDoorTo2FCorr</t>
+  </si>
+  <si>
+    <t>Finde den Schlüssel für die Kinderzimmertür und schließe diese damit auf.</t>
+  </si>
+  <si>
+    <t>1_01_DOOR_UNLOCKED</t>
+  </si>
+  <si>
+    <t>StoryInteractable_DoorLocked, DragItemZone_UnlockDoorTo2FCorr</t>
+  </si>
+  <si>
+    <t>StoryInteractable_FridgePart1, StoryInteractable_StorageLocked, StoryInteractable_TV, StoryInteractable_Plant, LockInteractable_ClosetDummy, DoorInteractable_To1FCorridor, DragItemZone_UnlockStorageRoom</t>
+  </si>
+  <si>
+    <t>StoryInteractable_StorageLockedJekko, DragItemZone_UnlockStorageRoom</t>
+  </si>
+  <si>
+    <t>StoryInteractable_ClosetLocked, StoryInteractable_Bed, StoryInteractable_DrawerLocked, StoryInteractable_DoorLocked, BlackscreenInteractable_Lvl1Intro, StoryInteractable_PC, DragItemZone_UnlockDoorTo2FCorr, DragItemZone_UnlockChildrenDrawer</t>
+  </si>
+  <si>
+    <t>DragItemZone_UnlockChildrenDrawer</t>
+  </si>
+  <si>
+    <t>1_05_CHILDDRAWERUNLOCK</t>
+  </si>
+  <si>
+    <t>StoryInteractable_DrawerLockedJekko; DragItemZone_UnlockChildrenDrawer</t>
+  </si>
+  <si>
+    <t>DoorInteractable_To2FBathroom, StoryInteractable_3rdFloorLockedLvl2, ContainerInteractable_DrawerBath2F, DragItemZone_Unlock3F</t>
+  </si>
+  <si>
+    <t>2_02_UNLOCK3F</t>
+  </si>
+  <si>
+    <t>DragItemZone_Unlock3F</t>
+  </si>
+  <si>
+    <t>SpriteToggleInteractable_Chain, SpriteToggleInteractable_OldFG, SpriteToggleInteractable_NewFG, BlackscreenInteractable_3FOff</t>
+  </si>
+  <si>
+    <t>BlackscreenInteractable_3FOff, SpriteToggleInteractable_Chain, SpriteToggleInteractable_OldFG, SpriteToggleInteractable_NewFG</t>
+  </si>
+  <si>
+    <t>StoryInteractable_ShadowEncounter2, ReadableInteractable_Remember, ReadableInteractable_RememberMAN</t>
+  </si>
+  <si>
+    <t>2_03_CELLARHINT</t>
+  </si>
+  <si>
+    <t>ReadableInteractable_Remember</t>
+  </si>
+  <si>
+    <t>StoryInteractable_FatherPart2, StoryInteractable_CellarLockedLvl1Jekko</t>
+  </si>
+  <si>
+    <t>1_08_PHONEREPAIRED</t>
+  </si>
+  <si>
+    <t>DragItemZone_Phone</t>
+  </si>
+  <si>
+    <t>1_08_WAITFORCABLE</t>
+  </si>
+  <si>
+    <t>1_08_ATTACHCABLE</t>
+  </si>
+  <si>
+    <t>DragItemZone_Phone, StoryInteractable_PhoneGenericLvl1</t>
+  </si>
+  <si>
+    <t>SpriteToggleInteractable_PhoneCable</t>
+  </si>
+  <si>
+    <t>1_08_CABLEATTACHED</t>
+  </si>
+  <si>
+    <t>Bring das Kabel am Telefon an und bestell Jekko und Kara eine Pizza.</t>
+  </si>
+  <si>
+    <t>StoryInteractable_FridgePart2, StoryInteractable_PhoneGenericLvl1PreRiddle</t>
+  </si>
+  <si>
+    <t>DoorInteractable_ToLiving, DoorInteractable_To2FCorridor, StoryInteractable_CellarLockedLvl1,  StoryInteractable_PhoneGenericLvl1PreRiddle</t>
+  </si>
+  <si>
+    <t>StoryInteractable_ParentClosedLvl1Jekko, StoryInteractable_3FBathLockedCoinHint, DragItemZone_Unlock3FBathroom</t>
+  </si>
+  <si>
+    <t>StoryInteractable_KaraPostHorrorCutscene, StoryInteractable_3FBathLocked</t>
+  </si>
+  <si>
+    <t>2_08_PREPARE_3FCORR</t>
+  </si>
+  <si>
+    <t>2_08_3FBATHUNLOCK</t>
+  </si>
+  <si>
+    <t>DragItemZone_Unlock3FBathroom</t>
+  </si>
+  <si>
+    <t>2_08_UNLOCK3FBATH</t>
+  </si>
+  <si>
+    <t>DoorInteractable_To3FBathroom</t>
+  </si>
+  <si>
+    <t>StoryInteractable_3FBathLockedCoinHint, DragItemZone_Unlock3FBathroom</t>
+  </si>
+  <si>
+    <t>2_08_3FBATHENTERED</t>
+  </si>
+  <si>
+    <t>2_09_PREPARE_3FBATH</t>
+  </si>
+  <si>
+    <t>DoorInteractable_To3FCorridor, ContainerInteractable_DrawerBath3F, StoryInteractable_Shower3F, StoryInteractable_Toilet3F, StoryInteractable_Heizung3F</t>
+  </si>
+  <si>
+    <t>2_09_AUTOOBTAINKEY</t>
+  </si>
+  <si>
+    <t>SUPER_GLUE</t>
+  </si>
+  <si>
+    <t>ObtainItemInteractable_RemoveBrokenKey, ObtainItemInteractable_AddRepairedKey, StoryInteractable_KeyRepaired</t>
+  </si>
+  <si>
+    <t>2_09_KEYREPAIREDCSFIN</t>
+  </si>
+  <si>
+    <t>StoryInteractable_KeyRepaired</t>
+  </si>
+  <si>
+    <t>2_09_POSTKEYOBTAINED</t>
+  </si>
+  <si>
+    <t>Schließe die Schlafzimmertür auf und betritt das Zimmer.</t>
+  </si>
+  <si>
+    <t>DoorInteractable_ToParentsRoom</t>
+  </si>
+  <si>
+    <t>DragItemZone_UnlockParents</t>
+  </si>
+  <si>
+    <t>2_09_PARENTSUNLOCKED</t>
+  </si>
+  <si>
+    <t>DragItemZone_UnlockParents, StoryInteractable_ParentsClosedLvl1Jekko</t>
+  </si>
+  <si>
+    <t>2_10_PREPARE_PARENTS</t>
+  </si>
+  <si>
+    <t>2_09_ENTEREDPARENTS</t>
+  </si>
+  <si>
+    <t>StoryInteractable_Mirror, StoryInteractable_Bed, StoryInteractable_ClosetLockedLeft, StoryInteractable_ClosetLockedRight, DoorInteractable_To2FCorr, ContainerInteractable_Drawer</t>
+  </si>
+  <si>
+    <t>KEY_CELLAR</t>
+  </si>
+  <si>
+    <t>2_10_PARENTSENTER</t>
+  </si>
+  <si>
+    <t>StoryInteractable_ParentsRoomFirstTIme</t>
+  </si>
+  <si>
+    <t>2_10_PARENTSFIRSTFIN</t>
+  </si>
+  <si>
+    <t>2_10_CELLARKEYFOUND</t>
+  </si>
+  <si>
+    <t>2_10_KEYFOUNDFIN</t>
+  </si>
+  <si>
+    <t>2_11_PRECELLAR</t>
+  </si>
+  <si>
+    <t>DragItemZone_UnlockCellar</t>
+  </si>
+  <si>
+    <t>2_11_CELLARUNLOCKED</t>
+  </si>
+  <si>
+    <t>DragItemZone_UnlockCellar, StoryInteractable_CellarLockedLvl1Jekko</t>
+  </si>
+  <si>
+    <t>StoryInteractable_EnterCellarLvl2, BlackscreenInteractable_Lvl2Fin</t>
+  </si>
+  <si>
+    <t>2_11_BSON</t>
+  </si>
+  <si>
+    <t>BlackscreenInteractable_Lvl2Fin</t>
+  </si>
+  <si>
+    <t>2_11_TELEPORT</t>
+  </si>
+  <si>
+    <t>DoorInteractable_AutoLvl2Fin</t>
+  </si>
+  <si>
+    <t>2_11_TELEPORTFIN</t>
+  </si>
+  <si>
+    <t>3_1_BSOFF</t>
+  </si>
+  <si>
+    <t>BlackscreenInteractable_Lvl3Start</t>
+  </si>
+  <si>
+    <t>3_1_STARTCS</t>
+  </si>
+  <si>
+    <t>StoryInteractable_Lvl3Start</t>
+  </si>
+  <si>
+    <t>3_1_STARTCSFIN</t>
+  </si>
+  <si>
+    <t>StoryInteractable_ScissorsFound, StoryInteractable_3rdFloorLockedJekko</t>
+  </si>
+  <si>
+    <t>DragItemZone_Unlock3F, StoryInteractable_3rdFloorLockedJekko</t>
+  </si>
+  <si>
+    <t>StoryInteractable_StorageKeyObtained, DragItemZone_UnlockStorageRoom</t>
+  </si>
+  <si>
+    <t>1_05_STORAGEUNLOCKED</t>
+  </si>
+  <si>
+    <t>ContainerInteractable_Storage</t>
+  </si>
+  <si>
+    <t>DragItemZone_UnlockStorageRoom</t>
+  </si>
+  <si>
+    <t>1_05_UNLOCKSTORAGE</t>
+  </si>
+  <si>
+    <t>3_1_PREPARECELLARLONG</t>
+  </si>
+  <si>
+    <t>ContainerInteractable_Closet1, ContainerInteractable_Closet2, ContainerInteractable_Closet3, LockInteractable_UnlockCloset4, StoryInteractable_Lvl3StartPt2</t>
+  </si>
+  <si>
+    <t>3_1_STARTPT2FIN</t>
+  </si>
+  <si>
+    <t>StoryInteractable_Lvl3StartPt2</t>
+  </si>
+  <si>
+    <t>Erkunde den Keller.</t>
+  </si>
+  <si>
+    <t>3_1_UNLOCKCLOSET4</t>
+  </si>
+  <si>
+    <t>LockInteractable_UnlockCloset4</t>
+  </si>
+  <si>
+    <t>ContainerInteractable_Closet4</t>
+  </si>
+  <si>
+    <t>GLAS_SHARD</t>
+  </si>
+  <si>
+    <t>3_1_FLESH_BSON</t>
+  </si>
+  <si>
+    <t>3_1_FLESHTELEPORT</t>
+  </si>
+  <si>
+    <t>3_2_FLESH_BSOFF</t>
+  </si>
+  <si>
+    <t>BlackscreenInteractable_FleshOn</t>
+  </si>
+  <si>
+    <t>3_1_FLESHBSON</t>
+  </si>
+  <si>
+    <t>DoorInteractable_FleshAutoTeleport</t>
+  </si>
+  <si>
+    <t>StoryInteractable_ShardObtained</t>
+  </si>
+  <si>
+    <t>3_2_SHARDOBTFIN</t>
+  </si>
+  <si>
+    <t>StoryInteractable_ShardObtained; BlackscreenInteractable_FleshOFF</t>
+  </si>
+  <si>
+    <t>3_2_SKINDOOROPENED</t>
+  </si>
+  <si>
+    <t>DragItemZone_SkinDoor</t>
+  </si>
+  <si>
+    <t>StoryInteractable_SkinDoor, DragItemZone_SkinDoor</t>
+  </si>
+  <si>
+    <t>3_2_SKINDOORBSON</t>
+  </si>
+  <si>
+    <t>BlackscreenInteractable_SkinDoorOn</t>
+  </si>
+  <si>
+    <t>DragItemZone_SkinDoor, StoryInteractable_SkinDoor</t>
+  </si>
+  <si>
+    <t>3_2_SKINDOORBSOFF</t>
+  </si>
+  <si>
+    <t>3_3_CARVINGROOM</t>
+  </si>
+  <si>
+    <t>3_2_SKINBSON</t>
+  </si>
+  <si>
+    <t>3_2_SKINBSOFF</t>
+  </si>
+  <si>
+    <t>BlackscreenInteractable_SkinDoorOFF</t>
+  </si>
+  <si>
+    <t>Erkunde den "Keller".</t>
+  </si>
+  <si>
+    <t>StoryInteractable_SkinRoom</t>
+  </si>
+  <si>
+    <t>3_3_SKINROOMCSFIN</t>
+  </si>
+  <si>
+    <t>3_3_WALLINTERACT</t>
+  </si>
+  <si>
+    <t>Betritt das Schnitzzimmer.</t>
+  </si>
+  <si>
+    <t>Folge deinem Willen und "schreib" etwas auf die Wand.</t>
+  </si>
+  <si>
+    <t>StoryInteractable_SkinWall</t>
+  </si>
+  <si>
+    <t>3_3_SKINWALLFIN</t>
+  </si>
+  <si>
+    <t>3_3_CARVINGBSON</t>
+  </si>
+  <si>
+    <t>3_3_CARVINGBSOFF</t>
+  </si>
+  <si>
+    <t>BlackscreenInteractable_SkinWallOn</t>
+  </si>
+  <si>
+    <t>BlackscreenInteractable_SkinWallOff, SpriteToggleInteractable_SkinWall</t>
+  </si>
+  <si>
+    <t>3_3_POSTCARVINGCS</t>
+  </si>
+  <si>
+    <t>3_3_WALLBSON</t>
+  </si>
+  <si>
+    <t>3_3_WALLBSOFF</t>
+  </si>
+  <si>
+    <t>BlackscreenInteractable_SkinWallOFF</t>
+  </si>
+  <si>
+    <t>StoryInteractable_SkinWallPostCarved</t>
+  </si>
+  <si>
+    <t>3_3_POSTCARVEDFIN</t>
+  </si>
+  <si>
+    <t>BlackscreenInteractable_SkinDoorOff, DoorInteractable_CarvingAutoTeleport</t>
   </si>
 </sst>
 </file>
@@ -798,7 +1128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -818,6 +1148,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1132,7 +1465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7864EAA7-D267-4D29-92C1-8FC2892D9B09}">
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I119"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="25.7109375" customWidth="1"/>
@@ -1176,13 +1509,13 @@
         <v>6</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="72" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="96" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1193,12 +1526,12 @@
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>31</v>
+        <v>223</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>12</v>
@@ -1213,20 +1546,20 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -1244,7 +1577,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>13</v>
@@ -1274,17 +1607,17 @@
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="36" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -1299,12 +1632,15 @@
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="I7" s="1" t="s">
-        <v>26</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:9" ht="36" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -1314,22 +1650,22 @@
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -1341,18 +1677,18 @@
         <v>2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I9" s="1"/>
     </row>
@@ -1364,22 +1700,22 @@
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I10" s="1"/>
     </row>
@@ -1391,49 +1727,49 @@
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2">
+        <v>3</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" ht="36" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>1</v>
-      </c>
-      <c r="B12" s="2">
-        <v>3</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" ht="72" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="84" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>1</v>
       </c>
@@ -1441,20 +1777,20 @@
         <v>4</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I13" s="1"/>
     </row>
@@ -1466,20 +1802,20 @@
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I14" s="1"/>
     </row>
@@ -1491,20 +1827,20 @@
         <v>4</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="I15" s="1"/>
     </row>
@@ -1516,20 +1852,20 @@
         <v>4</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="36" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>1</v>
       </c>
@@ -1537,22 +1873,22 @@
         <v>4</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>57</v>
+        <v>244</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="36" x14ac:dyDescent="0.25">
@@ -1563,21 +1899,21 @@
         <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="24" x14ac:dyDescent="0.25">
@@ -1588,24 +1924,21 @@
         <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>73</v>
+        <v>294</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>1</v>
       </c>
@@ -1613,43 +1946,41 @@
         <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="G20" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
         <v>1</v>
       </c>
       <c r="B21" s="2">
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="1:9" ht="36" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>1</v>
       </c>
@@ -1657,22 +1988,22 @@
         <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" ht="36" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>1</v>
       </c>
@@ -1680,47 +2011,49 @@
         <v>5</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="1" t="s">
         <v>77</v>
       </c>
+      <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
+        <v>75</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="I23" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>91</v>
+        <v>226</v>
       </c>
       <c r="F24" s="1"/>
-      <c r="G24" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I24" s="1"/>
-    </row>
-    <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>1</v>
       </c>
@@ -1728,47 +2061,49 @@
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D25" s="1"/>
+        <v>80</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="E25" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>99</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="F25" s="1"/>
       <c r="G25" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="I25" s="1"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>95</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>1</v>
       </c>
@@ -1776,20 +2111,20 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E27" s="1"/>
+        <v>87</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="F27" s="1"/>
-      <c r="G27" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="28" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
@@ -1799,20 +2134,18 @@
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>100</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="I28" s="1"/>
     </row>
@@ -1821,29 +2154,27 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="F29" s="1"/>
       <c r="G29" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="I29" s="1"/>
     </row>
-    <row r="30" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="36" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>1</v>
       </c>
@@ -1851,95 +2182,94 @@
         <v>8</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>109</v>
+        <v>238</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>110</v>
+        <v>237</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F30" s="1"/>
+        <v>95</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>243</v>
+      </c>
       <c r="G30" s="1" t="s">
-        <v>111</v>
+        <v>236</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="I30" s="1"/>
+        <v>237</v>
+      </c>
     </row>
     <row r="31" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>112</v>
+        <v>239</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>114</v>
+        <v>241</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F31" s="1"/>
+        <v>240</v>
+      </c>
       <c r="G31" s="1" t="s">
-        <v>113</v>
+        <v>242</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>114</v>
+        <v>241</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D33" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="E33" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>119</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="F33" s="1"/>
       <c r="G33" s="1" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>23</v>
+        <v>101</v>
       </c>
       <c r="I33" s="1"/>
     </row>
@@ -1948,75 +2278,75 @@
         <v>2</v>
       </c>
       <c r="B34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="I34" s="1"/>
     </row>
-    <row r="35" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>2</v>
       </c>
       <c r="B35" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="I35" s="1"/>
     </row>
-    <row r="36" spans="1:9" ht="36" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>2</v>
       </c>
       <c r="B36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>130</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="D36" s="1"/>
       <c r="E36" s="1" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1" t="s">
-        <v>132</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" s="1"/>
     </row>
     <row r="37" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
@@ -2026,20 +2356,20 @@
         <v>2</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="I37" s="1"/>
     </row>
@@ -2051,26 +2381,24 @@
         <v>2</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>153</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="F38" s="1"/>
       <c r="G38" s="1" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="I38" s="1"/>
     </row>
-    <row r="39" spans="1:9" ht="36" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="48" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>2</v>
       </c>
@@ -2078,24 +2406,24 @@
         <v>2</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>142</v>
+        <v>227</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="1:9" ht="36" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>2</v>
       </c>
@@ -2103,24 +2431,24 @@
         <v>2</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>146</v>
+        <v>292</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="I40" s="1"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>2</v>
       </c>
@@ -2128,22 +2456,22 @@
         <v>2</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>151</v>
+        <v>228</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>149</v>
+        <v>229</v>
       </c>
       <c r="I41" s="1"/>
     </row>
@@ -2152,73 +2480,75 @@
         <v>2</v>
       </c>
       <c r="B42" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E42" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>293</v>
+      </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="I42" s="1"/>
     </row>
-    <row r="43" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="48" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>2</v>
       </c>
       <c r="B43" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>158</v>
+        <v>230</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="I43" s="1"/>
     </row>
-    <row r="44" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="48" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>2</v>
       </c>
       <c r="B44" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>161</v>
+        <v>231</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="I44" s="1"/>
     </row>
@@ -2230,74 +2560,70 @@
         <v>3</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>165</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="I45" s="1"/>
     </row>
-    <row r="46" spans="1:9" ht="36" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>2</v>
       </c>
       <c r="B46" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>168</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="F46" s="1"/>
       <c r="G46" s="1" t="s">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="I46" s="1"/>
     </row>
-    <row r="47" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="84" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>2</v>
       </c>
       <c r="B47" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>179</v>
+        <v>232</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="I47" s="1"/>
     </row>
@@ -2306,100 +2632,101 @@
         <v>2</v>
       </c>
       <c r="B48" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>185</v>
+        <v>234</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1" t="s">
-        <v>187</v>
+        <v>233</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>186</v>
+        <v>234</v>
       </c>
       <c r="I48" s="1"/>
     </row>
-    <row r="49" spans="1:9" ht="48" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>2</v>
       </c>
       <c r="B49" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>183</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="F49" s="1"/>
       <c r="G49" s="1" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I49" s="1"/>
-    </row>
-    <row r="50" spans="1:9" ht="48" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>2</v>
       </c>
       <c r="B50" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>190</v>
+        <v>154</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F50" s="1"/>
+        <v>235</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>151</v>
+      </c>
       <c r="G50" s="1" t="s">
-        <v>191</v>
+        <v>155</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="1:9" ht="48" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>2</v>
       </c>
       <c r="B51" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>193</v>
+        <v>157</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F51" s="1"/>
+        <v>161</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="G51" s="1" t="s">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="I51" s="1"/>
     </row>
@@ -2408,23 +2735,23 @@
         <v>2</v>
       </c>
       <c r="B52" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="1" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="I52" s="1"/>
     </row>
@@ -2433,75 +2760,79 @@
         <v>2</v>
       </c>
       <c r="B53" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F53" s="1"/>
+        <v>167</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="G53" s="1" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>203</v>
+        <v>170</v>
       </c>
       <c r="I53" s="1"/>
     </row>
-    <row r="54" spans="1:9" ht="36" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="48" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>2</v>
       </c>
       <c r="B54" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D54" s="1"/>
+        <v>174</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>172</v>
+      </c>
       <c r="E54" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="36" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I54" s="1"/>
+    </row>
+    <row r="55" spans="1:9" ht="48" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>2</v>
       </c>
       <c r="B55" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1" t="s">
-        <v>208</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F55" s="1"/>
       <c r="G55" s="1" t="s">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="I55" s="1"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>2</v>
       </c>
@@ -2509,24 +2840,24 @@
         <v>6</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="I56" s="1"/>
     </row>
-    <row r="57" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="48" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>2</v>
       </c>
@@ -2534,24 +2865,24 @@
         <v>6</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1" t="s">
-        <v>214</v>
+        <v>184</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="I57" s="1"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="36" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>2</v>
       </c>
@@ -2559,24 +2890,22 @@
         <v>6</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>216</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="D58" s="1"/>
       <c r="E58" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="I58" s="1"/>
-    </row>
-    <row r="59" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="36" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>2</v>
       </c>
@@ -2584,24 +2913,24 @@
         <v>6</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>218</v>
+        <v>187</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F59" s="1"/>
+        <v>188</v>
+      </c>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1" t="s">
+        <v>190</v>
+      </c>
       <c r="G59" s="1" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="I59" s="1"/>
     </row>
-    <row r="60" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>2</v>
       </c>
@@ -2609,20 +2938,20 @@
         <v>6</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="I60" s="1"/>
     </row>
@@ -2634,45 +2963,45 @@
         <v>6</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1" t="s">
-        <v>229</v>
+        <v>196</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="I61" s="1"/>
     </row>
-    <row r="62" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>2</v>
       </c>
       <c r="B62" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="I62" s="1"/>
     </row>
@@ -2681,234 +3010,1079 @@
         <v>2</v>
       </c>
       <c r="B63" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="I63" s="1"/>
     </row>
-    <row r="64" spans="1:9" ht="36" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>2</v>
       </c>
       <c r="B64" s="2">
+        <v>6</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="I64" s="1"/>
+    </row>
+    <row r="65" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>2</v>
+      </c>
+      <c r="B65" s="2">
+        <v>6</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I65" s="1"/>
+    </row>
+    <row r="66" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>2</v>
+      </c>
+      <c r="B66" s="2">
         <v>7</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
-        <v>2</v>
-      </c>
-      <c r="B65" s="2">
+      <c r="C66" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="I66" s="1"/>
+    </row>
+    <row r="67" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>2</v>
+      </c>
+      <c r="B67" s="2">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="I67" s="1"/>
+    </row>
+    <row r="68" spans="1:9" ht="36" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>2</v>
+      </c>
+      <c r="B68" s="2">
         <v>8</v>
       </c>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
-        <v>2</v>
-      </c>
-      <c r="B66" s="2">
+      <c r="C68" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="I68" s="1"/>
+    </row>
+    <row r="69" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>2</v>
+      </c>
+      <c r="B69" s="2">
         <v>8</v>
       </c>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
-        <v>2</v>
-      </c>
-      <c r="B67" s="2">
+      <c r="C69" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="I69" s="1"/>
+    </row>
+    <row r="70" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>2</v>
+      </c>
+      <c r="B70" s="2">
         <v>9</v>
       </c>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
-        <v>2</v>
-      </c>
-      <c r="B68" s="2">
-        <v>9</v>
-      </c>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
-        <v>2</v>
-      </c>
-      <c r="B69" s="2">
-        <v>10</v>
-      </c>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
-        <v>2</v>
-      </c>
-      <c r="B70" s="2">
-        <v>10</v>
-      </c>
-      <c r="D70" s="1"/>
+      <c r="C70" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>256</v>
+      </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I70" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="36" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B71" s="2">
-        <v>1</v>
-      </c>
-      <c r="D71" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>259</v>
+      </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
+      <c r="G71" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>261</v>
+      </c>
       <c r="I71" s="1"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
+    <row r="72" spans="1:9" ht="36" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>2</v>
+      </c>
+      <c r="B72" s="2">
+        <v>9</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>265</v>
+      </c>
       <c r="I72" s="1"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
+    <row r="73" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>2</v>
+      </c>
+      <c r="B73" s="2">
+        <v>9</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>267</v>
+      </c>
       <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
+      <c r="G73" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>264</v>
+      </c>
       <c r="I73" s="1"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D74" s="1"/>
+    <row r="74" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>2</v>
+      </c>
+      <c r="B74" s="2">
+        <v>10</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>273</v>
+      </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
+      <c r="G74" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="72" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>2</v>
+      </c>
+      <c r="B75" s="2">
+        <v>10</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>273</v>
+      </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
+      <c r="I75" s="1" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D76" s="1"/>
+      <c r="A76" s="2">
+        <v>2</v>
+      </c>
+      <c r="B76" s="2">
+        <v>10</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>188</v>
+      </c>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
+      <c r="G76" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>188</v>
+      </c>
       <c r="I76" s="1"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
+      <c r="A77" s="2">
+        <v>2</v>
+      </c>
+      <c r="B77" s="2">
+        <v>11</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="I77" s="1"/>
+    </row>
+    <row r="78" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>2</v>
+      </c>
+      <c r="B78" s="2">
+        <v>11</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>280</v>
+      </c>
       <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
+      <c r="G78" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>283</v>
+      </c>
       <c r="I78" s="8"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="8"/>
-      <c r="I80" s="8"/>
-    </row>
-    <row r="81" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="8"/>
-    </row>
-    <row r="82" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="8"/>
+    <row r="79" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>2</v>
+      </c>
+      <c r="B79" s="2">
+        <v>11</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="I79" s="1"/>
+    </row>
+    <row r="80" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>3</v>
+      </c>
+      <c r="B80" s="2">
+        <v>1</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="I80" s="1"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>3</v>
+      </c>
+      <c r="B81" s="2">
+        <v>1</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="I81" s="1"/>
+    </row>
+    <row r="82" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>3</v>
+      </c>
+      <c r="B82" s="2">
+        <v>1</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="I82" s="1"/>
+    </row>
+    <row r="83" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>3</v>
+      </c>
+      <c r="B83" s="2">
+        <v>1</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I83" s="2"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>3</v>
+      </c>
+      <c r="B84" s="2">
+        <v>1</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <v>3</v>
+      </c>
+      <c r="B85" s="2">
+        <v>1</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="I85" s="2"/>
+    </row>
+    <row r="86" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>3</v>
+      </c>
+      <c r="B86" s="9">
+        <v>1</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I86" s="2"/>
+    </row>
+    <row r="87" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>3</v>
+      </c>
+      <c r="B87" s="9">
+        <v>2</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I87" s="2"/>
+    </row>
+    <row r="88" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>3</v>
+      </c>
+      <c r="B88" s="9">
+        <v>2</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="I88" s="2"/>
+    </row>
+    <row r="89" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <v>3</v>
+      </c>
+      <c r="B89" s="9">
+        <v>2</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I89" s="2"/>
+    </row>
+    <row r="90" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>3</v>
+      </c>
+      <c r="B90" s="9">
+        <v>2</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="I90" s="2"/>
+    </row>
+    <row r="91" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
+        <v>3</v>
+      </c>
+      <c r="B91" s="9">
+        <v>3</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I91" s="2"/>
+    </row>
+    <row r="92" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>3</v>
+      </c>
+      <c r="B92" s="9">
+        <v>3</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="I92" s="2"/>
+    </row>
+    <row r="93" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>3</v>
+      </c>
+      <c r="B93" s="9">
+        <v>3</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="I93" s="2"/>
+    </row>
+    <row r="94" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>3</v>
+      </c>
+      <c r="B94" s="9">
+        <v>3</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="I94" s="2"/>
+    </row>
+    <row r="95" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>3</v>
+      </c>
+      <c r="B95" s="9">
+        <v>3</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="I95" s="2"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>3</v>
+      </c>
+      <c r="B96" s="9"/>
+      <c r="C96" s="9"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="2"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>3</v>
+      </c>
+      <c r="B97" s="9"/>
+      <c r="C97" s="9"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="2"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>3</v>
+      </c>
+      <c r="B98" s="9"/>
+      <c r="C98" s="9"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="2"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>3</v>
+      </c>
+      <c r="B99" s="9"/>
+      <c r="C99" s="9"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="2"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>3</v>
+      </c>
+      <c r="B100" s="9"/>
+      <c r="C100" s="9"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="2"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>3</v>
+      </c>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="2"/>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>3</v>
+      </c>
+      <c r="B102" s="9"/>
+      <c r="C102" s="9"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
+        <v>3</v>
+      </c>
+      <c r="B103" s="9"/>
+      <c r="C103" s="9"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>3</v>
+      </c>
+      <c r="B104" s="9"/>
+      <c r="C104" s="9"/>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1"/>
+      <c r="E107" s="1"/>
+      <c r="F107" s="1"/>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1"/>
+      <c r="E108" s="1"/>
+      <c r="F108" s="1"/>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="2">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1"/>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="2">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1"/>
+      <c r="F114" s="1"/>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="2">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1"/>
+      <c r="E115" s="1"/>
+      <c r="F115" s="1"/>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="2">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1"/>
+      <c r="E116" s="1"/>
+      <c r="F116" s="1"/>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="2">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1"/>
+      <c r="E117" s="1"/>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="2">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1"/>
+      <c r="E118" s="1"/>
+      <c r="F118" s="1"/>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="2">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
